--- a/docs/待办-后续优化计划.xlsx
+++ b/docs/待办-后续优化计划.xlsx
@@ -1144,7 +1144,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1381,24 +1381,68 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>后续需求①（2026-09-17 现场）</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>**调完建议密度后、还在等新化验/新数据的那段时间，右边不应该给出建议值。**保持中卡片建议位显示「—」（灰显 + 悬停提示），副标题只留「密度计 X · 保持（等新化验/新数据）」。</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>hold 状态下内部是 rhoNew = rhoCur（「当前密度」被填进了建议位），显示出来就会被读成「建议 = 当前值 = 已达标」—— 这正是 9-12 那次误读的来源。没有建议可给的时候，界面上就不该出现建议数字。</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>overview.js 卡片：noAdvice = guide.hold &amp;&amp; !已达标 → 「—」；详情弹窗的「目标密度(本次一步)」「密度修正量」同样显示「—」并注明「保持中」。E2E 断言 HOLD_NO_ADVICE_ON_CARD / HOLD_NO_ADVICE_IN_MODAL。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>两种「保持」必须区分开</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>**达标保持**（灰分已在容差内）→ 仍显示当前密度，含义是「就保持这个值」；**守卫保持**（等新化验/同一份化验只动作一次）→ 不给建议值，显示「—」。</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>两者对操作员的含义完全不同：前者是结论（不用动），后者是等待（还判断不了）。9-12 的误读就是这两种被同一句话「达标保持」盖住了。</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>E2E 断言 ADVICE_MODAL_SHOWS_TARGET：有建议时弹窗必须给出目标值 —— 防止用「一律留空」这种假修法把功能改死。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>影响面</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>只改前端 app.js / overview.js；后端 compute_density_guidance 的 hold 与 hold_reason 一直由前端传入，口径未变，无需改动。</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>守卫状态是**前端算、后端用**的设计（state 传入 hold/hold_reason），所以这类修改天然不会造成前后端口径分叉。</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>pytest 104 全绿；五个 E2E 脚本（镜像写路径/决策日志/实测密度计/重介灰分闭环/驻留放行）在同一个临时库上顺序执行全部 PASS。</t>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>pytest 104 全绿；五个 E2E 脚本（镜像写路径/决策日志/实测密度计/重介灰分闭环/驻留放行，共 14 项断言）在同一个临时库上顺序执行全部 PASS。</t>
         </is>
       </c>
     </row>

--- a/docs/待办-后续优化计划.xlsx
+++ b/docs/待办-后续优化计划.xlsx
@@ -19,6 +19,7 @@
     <sheet name="写接口鉴权与事故复盘" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="实测密度计(仅展示)" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="密度建议守卫缺陷复盘" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="浮精影响分析-排除5月" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1454,6 +1455,234 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="66" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>浮精影响分析整页排除 2026-05 及以前数据：为什么去掉、去掉哪些、怎么守</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>议题</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>结论 / 做法</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>原因</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>守卫 / 将来怎么改</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>现场要求（2026-09-17）</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>「浮精影响分析」页面里 5 月份的数据去掉。落地为：**整页数据起点 = 2026-06-01**（联动趋势图、分布图、四张数值卡、明细表、卡片详情一致）。</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>现场看到的是：图上左侧孤零零几个 5 月点，中间一大段空白，8-9 月的点全挤在右边 —— 按真实时间比例分布的 X 轴把 3 个多月的空档都画了出来。</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>改 frontend/js/float.js 的 FLOAT_DATA_START 一处即可（现值 2026-06-01）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>数据事实</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>浮精一共 17 条：**5 月 5 条**（05-21~05-25）＋ **8/23~9/3 共 12 条**。5 月：煤量 26~27 t/h、灰分 8.2~10.4；8 月以后：19.5~22.6 t/h、灰分 9.4~14.0。</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>两段的煤量与灰分水平都不同 —— 不是同一工况，混在一张图里做趋势与波动统计没有意义。</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>如果将来确认 5 月属于可用的同一工况，把起点改回 2026-05-01 即可。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>为什么按「日期起点」而不是删掉那 5 条</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>过滤条件是「时间戳早于 2026-06-01 的记录不进本页」，不是按条数或按某几条 id 删。</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>按日期起点：① 将来补录 5 月数据也不会漏进来；② 一行常量可读可回退；③ 时间戳解析不出来的记录**保留**（宁可多显示，不静默丢数据）。</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>_pageData() 是本页唯一的数据入口（去重 + 起点过滤），四个调用点共用。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>作用范围（关键）</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>**仅本页展示与统计**。store.floatCoal 不动 —— 总灰分公式 resolveFloatAsh()、密度建议、粗灰模型训练照旧用全部浮精数据。</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>浮精灰分同时是总灰分公式的输入；若把它从 store 里删掉，会让密度建议与总灰分跟着变 —— 那是控制口径的改动，不是显示口径的改动，不能顺手做。</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>E2E 断言 STORE_KEEPS_MAY：页面过滤后 store 里 5 月记录仍在，且「本页条数 &lt; 全量条数」必须成立。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>实测效果</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>「动态波动范围」σ 从 **±0.092%**（含 5 月）降到 **±0.036%**（2026-06 起）—— 差 2.5 倍。</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>5 月那几条的浮精量与灰分把影响值的离散度整体抬高；卡片是给操作员看稳定性的，带着一段不同工况的数据等于虚报波动。</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>E2E 断言 RANGE_CARD_EXCLUDES_MAY：卡片显示值必须等于按页面口径算的 σ，且与「含 5 月」的 σ 明显不同（证明断言有牙，不是恒真）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>顺带修正的两个小瑕疵</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>① 卡片副标题原写「近24h标准差」，但代码实际用**全期**数据 → 改为「标准差（2026-06 起，不含5月）」，并在卡片详情里写明数据范围与条数；② 卡片详情的「最新一条」原用 data[length-1]（store 顺序不保证按时间）→ 改用 _latestByTime。</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>副标题与算法不一致属于「界面在说假话」，比缺功能更糟 —— 现场会按字面理解。</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>断言 RANGE_LABEL_HONEST（不含「近24h」、含数据起点）与 MODAL_SCOPE_AND_COUNT（详情里写数据范围且「共N条」= 页面口径条数）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>自动化守卫</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>backend/scripts/verify_float_may_excluded.js，10 项断言，已进 CI e2e 用例5。</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>其中 CHART_KEEPS_LATER 专门防「过滤写成全滤掉」：脚本会注入 8/25 与 9/1 两条记录，要求它们**必须**出现在图上。</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>全套断言：NAV_BUILDS_CHARTS / STORE_KEEPS_MAY / CHART_EXCLUDES_MAY / CHART_KEEPS_LATER / DIST_CHART_EXCLUDES_MAY / TABLE_EXCLUDES_MAY / RANGE_CARD_EXCLUDES_MAY / RANGE_LABEL_HONEST / MODAL_SCOPE_AND_COUNT / CLEANUP_OK。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>遗留</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>页面上那个「时间范围」输入框 + 查询按钮**仍然是装饰性的**（query() 并未按它过滤）。</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>这次没顺手接：接上要定义「默认范围」「与起点过滤的关系」「空结果怎么提示」等一串语义，属于另一个需求；混进来会把这次改动变复杂、也难验证。</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>要做的话另开一项：让 query() 读起止时间过滤 _pageData()，并让默认值 = 数据实际范围（否则默认「现在−24h」会把历史数据全滤掉、图变空）。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/docs/待办-后续优化计划.xlsx
+++ b/docs/待办-后续优化计划.xlsx
@@ -1145,7 +1145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1426,24 +1426,68 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>后续需求②（2026-09-17 现场）</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>**改过密度计之后，合并系统卡片最右侧的方向建议（「建议下调/建议上调」）应当隐藏。**保持中该处 `visibility:hidden`（占位隐藏，卡片不跳动）；有建议时恢复显示。</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>方向指示原先只看灰分偏差（dev 与容差比大小），**完全不看守卫状态** —— 于是同一张卡上左边建议密度已显示「—」、右边却还写着「建议下调」，自相矛盾。</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>overview.js：`dirEl.style.visibility = noAdvice ? 'hidden' : ''`。E2E 断言 HOLD_HIDES_DIRECTION（隐藏且 display 未被改动）／ADVICE_SHOWS_DIRECTION（有建议时重新可见且文本为「建议下调」）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>同一处顺带改的底部效果文案</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>卡片底部「预期效果」在保持中改为「保持中：等新化验/新数据后再判断」，不再写「适度降密可降低灰分，使偏差回归目标范围」。</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>那句效果说明本来是给「方向建议」做解释的；方向都藏了、解释还留着，等于换个地方继续给建议 —— 现场照样会照着做。</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>同一个 noAdvice 分支处理；ADVICE_SHOWS_DIRECTION 同时要求「有建议时」底部必须回到效果说明，防止改成「一直显示保持中」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>影响面</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>只改前端 app.js / overview.js；后端 compute_density_guidance 的 hold 与 hold_reason 一直由前端传入，口径未变，无需改动。</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C17" s="9" t="inlineStr">
         <is>
           <t>守卫状态是**前端算、后端用**的设计（state 传入 hold/hold_reason），所以这类修改天然不会造成前后端口径分叉。</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>pytest 104 全绿；五个 E2E 脚本（镜像写路径/决策日志/实测密度计/重介灰分闭环/驻留放行，共 14 项断言）在同一个临时库上顺序执行全部 PASS。</t>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>pytest 110 全绿；六个 E2E 脚本（镜像写路径/决策日志/实测密度计/重介灰分闭环/驻留放行与界面保持态/浮精排除5月，共 71 项断言）在同一临时库上顺序执行全部 PASS。</t>
         </is>
       </c>
     </row>

--- a/docs/待办-后续优化计划.xlsx
+++ b/docs/待办-后续优化计划.xlsx
@@ -20,6 +20,7 @@
     <sheet name="实测密度计(仅展示)" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="密度建议守卫缺陷复盘" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="浮精影响分析-排除5月" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="界面-移除右下角AI入口" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1727,6 +1728,168 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>移除界面右下角的 AI 解读助手入口：范围、可恢复性、验证</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>议题</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>结论 / 做法</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>原因</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>验证 / 以后怎么改</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>现场要求（2026-09-18）</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>把界面右下角的 AI 去掉。落地为：**摘掉页面上的挂载**，右下角不再出现悬浮「AI」按钮与聊天面板。</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>该入口是一个 `position:fixed; right:24px; bottom:24px` 的圆形按钮 + 400×540 面板，全页面常驻、盖在趋势图右下角。</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>只改 frontend/index.html 末尾的挂载两行。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>做法</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>删掉 `&lt;script src="js/assistant.js?v=1"&gt;&lt;/script&gt;` 与 `&lt;script&gt;Assistant.init();&lt;/script&gt;`，并在原处留一段注释写明「移除原因 + 恢复方法（把这两行加回来）」。</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Assistant 只在 `Assistant.init()` 被调用时才 buildUi() —— 不调用就完全不生成 DOM，所以摘挂载即可，无需改 js 或 CSS。</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>恢复：把注释里的两行加回 `&lt;/body&gt;` 之前即可（两行、零风险）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>为什么这次不删文件与后端接口</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>`frontend/js/assistant.js`、`style.css` 的 `.ai-*` 样式、后端 `/api/v1/assistant/ask` 与 `backend/tests/test_assistant.py` **全部保留未动**。</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>这套是另一个 agent 近期的提交（9ce6086 AI 助手升级、b087b2d 缓冲式+多供应商回退、a641a62 LLM 密钥文件支持），后端测试仍在 CI 的 pytest 里跑。只摘入口 = 零冲突、可两行恢复；删文件会让对方的后续改动直接撞车。</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>现场若确认**永久**不要：再删 js/assistant.js + `.ai-*` 样式块 + routers/assistant.py 与它的路由注册、test_assistant.py、verify_assistant.js，并同步更新本表。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>验证（一次性无头浏览器检查，不入库）</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>5 项断言全 PASS：NO_AI_BUTTON（无 #ai-assistant-btn）／NO_AI_PANEL（无 #ai-assistant-panel）／ASSISTANT_NOT_LOADED（`typeof Assistant === 'undefined'`，脚本清单里没有 assistant.js）／PAGE_STILL_OK（App.__ready、密度卡片、FloatPage 正常）／MANUAL_READD_STILL_WORKS（把脚本手动加回来，按钮立刻出现）。</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>最后一条是**反向证明**：说明被移除的是「自动挂载」，不是把 js 改坏了 —— 同时也验证了「两行即可恢复」这个承诺。</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>另核对：去掉 HTML 注释后，服务端首页的 12 个 `&lt;script src&gt;` 里已无 assistant.js，注释块闭合正常（注释内保留的两行不会被浏览器执行）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>影响面</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>只改 frontend/index.html；后端接口保留但页面已无调用方（接口本身只读、零写入）。</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>其余页面功能不受影响（PAGE_STILL_OK 断言覆盖总览卡片与浮精页脚本加载）。</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>本页暂无自动化守卫（CI 的 6 个 E2E 用例都不涉及该入口）——若希望「永远不要再出现」，可把 NO_AI_BUTTON 加进某个 E2E 脚本；但那样会让另一个 agent 正常恢复该功能时 CI 变红，故本轮未加。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/docs/待办-后续优化计划.xlsx
+++ b/docs/待办-后续优化计划.xlsx
@@ -21,6 +21,7 @@
     <sheet name="密度建议守卫缺陷复盘" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="浮精影响分析-排除5月" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="界面-移除右下角AI入口" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="测试脚本误写生产库-复盘" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1890,6 +1891,234 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="66" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>E2E 脚本误打到真实库：多了一条决策日志、密度被写成 1.485 —— 盘点、恢复、防复发</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>议题</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>事实 / 结论</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>原因</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>修法 / 守卫</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>发生了什么</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>为验证「7 个 E2E 用例能否像 CI 那样顺序通过」，我起了一个临时库服务并带 DMCS_ALLOW_REAL_DB=1 跑全套。结果**临时服务没绑上端口**（8000 已被生产服务占用，Start-Process 静默失败），脚本全部打到**真实库**。</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>后果：verify_decision_log.js 把密度写成 **1.485** 并新增一条 density_set 决策日志；其余脚本的写入没有落库（auto_state 各键 updated_at 仍是 9-18，未被今天触碰）。</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>发现方式：核对 densityDecisionLog 只有 2 条，其中 2026-09-19 14:15:35 那条 rhoNew=1.485 正是测试值；instrumentInputs.density.manualAt = 今天 14:15:36。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>影响面（逐项盘点）</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>**只有两处被改动**：① instrumentInputs.density.manual 1.53 → 1.485；② densityDecisionLog 多一条测试条目。</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>未变的项（逐项核对）：coal_records 152/17/360 条、ashTarget 8.5、heavyAshInput 7.5（9-18）、amountInputs.floatAmount 40（9-18）、autoState 在线值（9-10）、manual_entries 242 条。</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>证据：auto_state 表按键看 updated_at —— 只有 instrumentInputs / densityDecisionLog / autoState / amountInputs 被今天那次整库 PUT 触碰，其余键仍是 9-18 的时间戳。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>恢复</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>先备份数据库（sqlite3 backup API，WAL 下安全）：backend/data/backups/dense_medium-pollution-fix-20260919-141707-036.db；再把密度改回 **1.53**（manualAt 用 9-18 09:39:01 那次真实操作时刻）、删掉那条 1.485 的测试日志。</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>1.53 的依据：9-18 那条真实决策日志 rhoCur=1.53、autoState.density.v=1.53（在线层）。</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>恢复后复核：instrumentInputs = {density:{manual:1.53}}；densityDecisionLog 回到 1 条。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>根因①（脚本侧）</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>**verify_decision_log.js 一直没有非空库守卫** —— 其余 6 个脚本都有，唯独它没有，于是 allowReal 没设也照跑，直接在真实库上写密度。</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>它要验证的正是「设密度 → 产生决策日志 → 落库」这条链，天生就会写库；没有守卫 + 默认指向 8000 = 一旦有人在生产环境跑它，现场密度就被测试值改掉。</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>补守卫（与 verify_mirror_e2e.js 同规格文案，非空库拒跑并提示 DMCS_ALLOW_REAL_DB=1）；注意用 process.exitCode = 2; return; 而不是 process.exit(2) —— 后者在 CDP WebSocket 仍打开时会触发 Node 的 Assertion failed: !(handle-&gt;flags &amp; UV_HANDLE_CLOSING) 直接崩。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>根因②（操作侧）</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>我在 8000 上重复起服务且没有确认它是否真的绑定成功，还带了 allowReal。</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Start-Process 对端口冲突**不报错**，脚本于是连到了生产服务；而「带 allowReal」正是我自己为了模拟 CI 加的。</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>以后本地跑 E2E 固定用 **8010 + DMCS_URL**，并加**身份检查**：临时库 /api/v1/state 必须是空的（生产库是 152/17/360），不是空的中止不跑。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>防复发（脚本收尾）</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>三个会写密度的脚本现在跑完会**原样恢复**：verify_decision_log.js（密度层 + 守卫书签）、verify_heavy_ash_source.js、verify_dwell_bypass.js（密度层/重介灰分/开关/闩锁/变动时刻）。</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>测试脚本改现场输入，不该靠「记得用临时库」这种纪律兜着 —— 让脚本自己把改动收干净，才是可继承的做法。</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>各自新增断言：决策日志脚本 RESTORE: PASS；另两个 STATE_RESTORED: PASS（逐字段比对）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>本轮验证</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>临时库（8010，**身份检查 coarse=0/float=0/calc=0 → 确认是空临时库**）顺序跑 7 个用例：全部 PASS。</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>含新增断言：RESTORE: PASS（密度层恢复为 {manual:null}）、STATE_RESTORED: PASS ×2（密度层与重介灰分都回到 {manual:null}）。</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>CI 现在跑 7 个用例（第 7 个是粗精煤泥按日视图）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>遗留</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>verify_daily_view.js 仍无非空库守卫（它是只读脚本：只点导航、读图表，不写 store）。</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>不加守卫的理由：它唯一的写路径是「页面加载时整库镜像 PUT」，这与人工打开页面完全同路径，守卫拦不住也不该拦。</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>若仍要加：可照搬同一段守卫文案，代价是它对真实库运行时会直接拒跑（少一个现场诊断手段）。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/docs/待办-后续优化计划.xlsx
+++ b/docs/待办-后续优化计划.xlsx
@@ -22,6 +22,7 @@
     <sheet name="浮精影响分析-排除5月" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="界面-移除右下角AI入口" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="测试脚本误写生产库-复盘" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="遗留问题与建议(删仿真后)" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2119,6 +2120,372 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>删仿真落地后的 8 条遗留：理由、风险、建议做法（按优先级排序）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>编号</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>遗留问题</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>理由（为什么算遗留）</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>风险与影响</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>建议做法</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>优先级</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>现状证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>L-4</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>仪表读数取值收紧为 typeof==='number' 后，字符串数值会静默变 null</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>本轮把 latestCalcValue / latestBeltAsh 由 isFinite(+v) 改为 typeof v === 'number' &amp;&amp; isFinite(v)：字符串数值不再被强制转换。</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>若导入路径（三表 Excel / 补录 / 旧快照）里数值是字符串，这些读取会**静默变 null** → 501/502 读数消失 → 总灰分与建议密度跟着变；现场现象是「数据明明在库里，系统说没有」，且没有任何报错。这是本轮唯一可能造成静默数据缺失的改动。</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>① 先确认导入侧写入的一定是 number（在 import 归一化处显式强转或断言）；② 补一条测试：喂字符串数值的 calcLogs，断言取到数字或明确报错（不容许静默 null）；③ 若确认历史数据里有字符串，加一次性归一化迁移。</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>本次 grep backend/tests 全量筛 string/字符串 → 无任何相关用例</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>L-1</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>新 Excel 生成器依赖 Codex 私有运行时，换机器/CI 无法复现</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>generate_optimization_plan_xlsx.py 只是包装器：它调用 ~/.cache/codex-runtimes/codex-primary-runtime/dependencies 下的 node 与 @oai/artifact-tool，找不到就直接 SystemExit。</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>违反仓库约定「docs 的 Excel 一律由 backend/scripts/generate_*.py 生成、便于复现」；我这边和 CI 都重跑不了 → 文档与代码将无法同步演进，以后要么手改 xlsx（违反约定），要么找那台机器。</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>用 openpyxl 重写为自洽生成器（照 generate_todo_plan_xlsx.py 的样式）；.mjs 保留为历史产物并在文件头注明来源，不再作为生成入口。</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>该文件 36 行；第 20-27 行检查 runtime/node 与 @oai/artifact-tool，缺失即 raise SystemExit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>L-2</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>verify_api_errors.js 未进 CI</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>本轮新增的回归脚本覆盖「权限拒绝 / 守卫拒绝 / 数据库异常三类错误必须保留各自分类与原因（不被 api.js 的业务错误归一化吞掉）」，与本轮的鉴权改动配套，但目前只在本地手跑。</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>与 M-5/M-6 同类教训：不进 CI 的回归脚本会腐烂（verify_mirror_e2e.js 当年就这样长期无人执行）。这条恰好守着「权限拒绝不能被误报成业务错误」——现场排查时最容易踩。</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>加为第 8 个 e2e 用例（它不依赖后端与浏览器：node vm 里跑 api.js，秒级完成，成本极低）；或退一步在 CI 的 pytest 作业里加一步 node scripts/verify_api_errors.js。</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>本地实测 node scripts/verify_api_errors.js → 5 scenarios passed；ci.yml 7 个用例里没有它</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>L-3</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>删仿真对简报（brief）历史数值的影响未量化</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>brief.py 走 resolvers（同样不再含仿真），但简报金标准 backend/data/brief_js.json 未重新生成；而金标准路径里密度层是默认值 → 仿真本来就被门控关掉 → **金标准对这次改动不敏感**。</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>等于这次语义变更在简报这条链上「既没被验证、也没被守卫」。若某段历史里密度是真实来源（手动/实测录入），简报数值与改动前会不同，而没有任何断言覆盖；简报是现场每天看的东西，出错不易察觉。</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>① 用真实库快照跑一次 dump_brief_js.js + test_brief 对拍，明确「哪些行/列变化、变化多少」，把差异写进文档；② 补一条密度层为真实来源的简报用例（覆盖被门控打开的那条路径）。</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>本次只跑了 7 个 E2E + pytest；金标准文件（backend/data/*.json）未被重新生成</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>L-8</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>「调密度→看灰分怎么走」的演示能力随仿真消失</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>删仿真后，调密度的效果只在新化验/新仪表数据到达后才会体现（这正是新语义的本意），但界面上除了来源列改成「自动(502测量)」与采集页 tooltip 外，没有别的地方说明这一点。</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>现场培训/演示时那条链看起来是「死的」；操作员也可能误以为系统没反应 —— 这与 9-12 那次「改了化验建议不动」被误读是同一类风险（当时靠卡片副标题与详情弹窗讲清楚才解决）。</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>① 在合并系统卡片副标题或详情弹窗补一句「调密后需等新化验/新仪表数据」；② 若确需演示，另做一个**明确标注为仿真**的沙盘模式，不参与任何真实计算与决策日志。</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>本轮前端文案改动仅覆盖来源列与采集页 tooltip；卡片侧暂无同类提示</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>L-5</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>仿真残留配置与函数未清理（易误导后来者）</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>删仿真后，前端仍保留 DENSITY_GUIDE.simBaseRho / simK、getSimBaseRho()，并在 app.js:1775 一行里对外暴露；后端 density.py 的 DENSITY_GUIDE 也仍带 simBaseRho / simK。</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>后来者读到会以为仿真还在（甚至照着它「恢复」），也可能有人误用这两个常数去估算增益；同时它是「同一口径两份实现」的潜在分叉点（前后端各一份现已无用的定义）。</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>删除，或明确标注为历史（例如「2026-09-21 起仿真已移除，仅保留供旧数据解读」）；把 app.js:1775 那处对外暴露一并清掉；两处同时改，避免只删一侧。</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>grep 实测：app.js:1672-1676 / 1756 / 1764 / 1775；density.py:33-34</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>L-6</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>两个同名文档生成器并存</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>generate_optimization_plan_xlsx.py（Codex 包装器）与 .mjs（真正的构建器）同目录同名。</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>将来改文档只改一个就会漂移，也无法一眼判断哪个是权威来源。</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>与 L-1 合并处理：openpyxl 版作为唯一生成入口；.mjs 移到 docs/tools/ 或删除并留说明。</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>两文件分别 1641 / 11749 字节</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>L-7</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>新 Excel 未并入待办体系（分板块纪律）</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>docs/项目优化与后续计划-20260921.xlsx 是独立文件，没进 docs/待办-后续优化计划.xlsx 的分板块体系，与本表（遗留问题）也有职责重叠。</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>待办出现两处来源，容易漏项；现场/后来者不知道该看哪一份。</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>把它并入待办体系（新增「本轮改动 / 后续计划 / 实施建议」三个 Sheet），或明确声明它是阶段性报告、此后不再更新。</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>该文件 3 个 Sheet（本轮改动 10 行 / 后续计划 16 行 / 实施建议 13 行）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/docs/待办-后续优化计划.xlsx
+++ b/docs/待办-后续优化计划.xlsx
@@ -2442,39 +2442,39 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>L-7</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>新 Excel 未并入待办体系（分板块纪律）</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>docs/项目优化与后续计划-20260921.xlsx 是独立文件，没进 docs/待办-后续优化计划.xlsx 的分板块体系，与本表（遗留问题）也有职责重叠。</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>待办出现两处来源，容易漏项；现场/后来者不知道该看哪一份。</t>
-        </is>
-      </c>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>把它并入待办体系（新增「本轮改动 / 后续计划 / 实施建议」三个 Sheet），或明确声明它是阶段性报告、此后不再更新。</t>
-        </is>
-      </c>
-      <c r="F11" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="G11" s="9" t="inlineStr">
-        <is>
-          <t>该文件 3 个 Sheet（本轮改动 10 行 / 后续计划 16 行 / 实施建议 13 行）</t>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>新 Excel 未并入待办体系（分板块纪律）—— 【已决 2026-09-21】</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>现场决定（gpt6 判断）：**本待办表是持续维护入口**，那份报告保留为阶段快照；两者靠任务编号关联，不再复制出更多重复 Sheet。</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>已按此落地：报告的生成器里新增「编号对照与维护约定」Sheet（C01/C02 → 待办表条目映射），并写明「新需求一律进待办表、本表不再新增 Sheet」；报告生成器也已改为 openpyxl 自洽版（L-1）。</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>后续：新需求/新遗留只写本表；报告只在需要复盘 2026-09-21 那次优化时查阅。</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>已决</t>
+        </is>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>报告文件：docs/项目优化与后续计划-20260921.xlsx（4 Sheet，含编号对照）</t>
         </is>
       </c>
     </row>

--- a/docs/待办-后续优化计划.xlsx
+++ b/docs/待办-后续优化计划.xlsx
@@ -563,7 +563,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>基线之后剩余的全部待办：8 项可直接执行、8 项需你决策、4 项建议暂缓。每项都写明「原因」，原因是判断优先级和取舍的依据。</t>
+          <t>截至 2026-09-21 的持续待办。历史任务保留决策依据，本轮修复与待确认事项见「遗留问题与建议(删仿真后)」。</t>
         </is>
       </c>
     </row>
@@ -575,43 +575,43 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>可直接执行 10 项：缺陷修复 2 项 · 健壮性 3 项 · 文档 1 项 · 测试基建 1 项 · 数据治理 2 项 · 交付 1 项；需决策 8 项；建议暂缓 4 项。</t>
+          <t>本轮处理 8 项：数值补录、历史简报、采样落库、同步版本、皮带去重、来源时间、CI、模型验证。仍待现场数据 T-12/T-13，煤量关系见 L-13；D-1~D-3 继续暂缓。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>推荐批次 1（约 1.5h，零口径风险）</t>
+          <t>本轮：数据可靠性</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>T-1 浮精灰分解析失败不再当 0 · T-2 xlsx-lite 补 inlineStr/十六进制引用 · T-3 更新 frontend/AGENTS.md · T-4 补导入跨语言 golden。理由：两项是「静默产生假数据」的缺陷，两项是防后续踩坑的基建，改动都不触及算法与口径。</t>
+          <t>L-4 数值补录、L-3 历史简报、L-9 采样增量落库、L-11 皮带身份已修复。旧数字文本可读取，历史计算只使用当时可用的测量。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>推荐批次 2（约 2h）</t>
+          <t>本轮：同步与验证</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>T-5 年份常量化与跨年 · T-6 防回退守卫覆盖面 · T-7 存量影响值重算 · T-8 决策日志导出。理由：都依赖批次 1 的测试基建来兜底；T-7/T-8 直接影响现场能不能用这些数据。</t>
+          <t>L-10 版本冲突检查、L-8 来源与时间、L-2 CI 回归、L-12 训练折内预处理已实现。冲突时保留本地待同步数据，需核对后处理。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>推荐批次 3（需先决策）</t>
+          <t>下一步：现场验证</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>T-9 自定义日期格式对拍 · T-10 两个「新旧」判据统一。理由：T-10 的修法取决于「是否引入 revision」这个架构选择，先定方向再动手。</t>
+          <t>确认 501/502 煤量是否包含或互斥；提供 501 实测灰分及 8-30 真实化验；积累调密前后独立灰分样本。没有实测关系前，继续使用总灰分专家建议。</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>T-1：浮精灰分单元格为空白或写「-」「？」时，解析结果是 0%，并且作为一条真实记录入库，进而被 resolve_float_ash 取为最新值直接进入总灰分公式 —— 它会无声地拉低总灰分并影响密度建议，而现场从界面上看不出来。</t>
+          <t>优先确认煤量口径 L-13。501 若已包含 502，相加会重复计量；现场确认前保留现有公式，并将该假设单独列为待确认。</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>决策已全部落定并实现：Q-1/Q-2 推送与不拆分、Q-3 修去重键+覆盖计数、Q-4 常量不得驱动建议、Q-5 K 三态、Q-6 维持严格 24h 口径、Q-7 决定不做（场景已失效）、Q-8 暂缓（写明触发条件）。**代码侧已无待办**；只剩两类外部依赖：① 现场提供数据 T-12(501 灰分入库)、T-13(8-30 真实化验值)；② 暂缓项 D-1~D-4（已列明再启动条件）。</t>
+          <t>本轮代码修复已完成，待审查并在现场副本验证；未提交 commit、未推送。尚未完成：T-12/T-13 数据补齐、L-13 煤量口径、重介灰分与密度关系的数据积累。D-4 已转入 L-10 实施。</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>后端 parse_coarse_factors 的 errors 是字符串列表,前端 parseCoarseFactors 的 errors 是 {row,col,msg} 对象 —— 同一接口两种结构（见 T-14,低优先级）。已在新增的导入 golden 里按「只比条数」规避,待 T-14 统一后再改为逐条对拍。</t>
+          <t>新增 L-9~L-13：采样持久化、相同记录数的同步冲突、501/502 去重、模型验证数据泄漏及煤量口径。不能再以记录数或历史 CI 全绿代替业务核验。</t>
         </is>
       </c>
     </row>
@@ -2126,7 +2126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2182,7 +2182,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="92" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>L-4</t>
@@ -2190,22 +2190,22 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>仪表读数取值收紧为 typeof==='number' 后，字符串数值会静默变 null</t>
+          <t>数字文本被忽略</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>本轮把 latestCalcValue / latestBeltAsh 由 isFinite(+v) 改为 typeof v === 'number' &amp;&amp; isFinite(v)：字符串数值不再被强制转换。</t>
+          <t>手工补录原先直接保存 input.value 文本，读取时只接受 number。</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>若导入路径（三表 Excel / 补录 / 旧快照）里数值是字符串，这些读取会**静默变 null** → 501/502 读数消失 → 总灰分与建议密度跟着变；现场现象是「数据明明在库里，系统说没有」，且没有任何报错。这是本轮唯一可能造成静默数据缺失的改动。</t>
+          <t>已录入值可能被忽略，灰分与密度建议退回默认值。</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>① 先确认导入侧写入的一定是 number（在 import 归一化处显式强转或断言）；② 补一条测试：喂字符串数值的 calcLogs，断言取到数字或明确报错（不容许静默 null）；③ 若确认历史数据里有字符串，加一次性归一化迁移。</t>
+          <t>补录统一转为有限数字并校验范围；前后端兼容历史数字文本，拒绝空值、布尔和混合文本。</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
@@ -2215,11 +2215,11 @@
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>本次 grep backend/tests 全量筛 string/字符串 → 无任何相关用例</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
+          <t>已修复。补录 7.8、非法文本及旧数字字符串均有回归。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="92" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
           <t>L-1</t>
@@ -2227,22 +2227,22 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>新 Excel 生成器依赖 Codex 私有运行时，换机器/CI 无法复现</t>
+          <t>Excel 生成器可移植性</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>generate_optimization_plan_xlsx.py 只是包装器：它调用 ~/.cache/codex-runtimes/codex-primary-runtime/dependencies 下的 node 与 @oai/artifact-tool，找不到就直接 SystemExit。</t>
+          <t>旧入口依赖特定工作站运行时。</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>违反仓库约定「docs 的 Excel 一律由 backend/scripts/generate_*.py 生成、便于复现」；我这边和 CI 都重跑不了 → 文档与代码将无法同步演进，以后要么手改 xlsx（违反约定），要么找那台机器。</t>
+          <t>其它机器和 CI 不能复现计划表。</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>用 openpyxl 重写为自洽生成器（照 generate_todo_plan_xlsx.py 的样式）；.mjs 保留为历史产物并在文件头注明来源，不再作为生成入口。</t>
+          <t>保留仓库 Python 生成器，使用锁定依赖；本轮状态更新也纳入生成输入。</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
@@ -2252,11 +2252,11 @@
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>该文件 36 行；第 20-27 行检查 runtime/node 与 @oai/artifact-tool，缺失即 raise SystemExit</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
+          <t>此前已完成。本轮补充生成内容与待办状态。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="92" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
         <is>
           <t>L-2</t>
@@ -2264,22 +2264,22 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>verify_api_errors.js 未进 CI</t>
+          <t>前端回归未纳入 CI</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>本轮新增的回归脚本覆盖「权限拒绝 / 守卫拒绝 / 数据库异常三类错误必须保留各自分类与原因（不被 api.js 的业务错误归一化吞掉）」，与本轮的鉴权改动配套，但目前只在本地手跑。</t>
+          <t>API 错误分类脚本原先仅本地执行，pytest 的 Node 依赖也未显式安装。</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>与 M-5/M-6 同类教训：不进 CI 的回归脚本会腐烂（verify_mirror_e2e.js 当年就这样长期无人执行）。这条恰好守着「权限拒绝不能被误报成业务错误」——现场排查时最容易踩。</t>
+          <t>回归脚本可能不执行或静默跳过。</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>加为第 8 个 e2e 用例（它不依赖后端与浏览器：node vm 里跑 api.js，秒级完成，成本极低）；或退一步在 CI 的 pytest 作业里加一步 node scripts/verify_api_errors.js。</t>
+          <t>pytest 作业安装 Node 22，执行 API 错误和人工总灰分流程回归；缺 Node 的必要测试直接失败。</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -2289,11 +2289,11 @@
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>本地实测 node scripts/verify_api_errors.js → 5 scenarios passed；ci.yml 7 个用例里没有它</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
+          <t>已修复。API 回归包含版本冲突和成功版本返回。远端 CI 需提交后运行。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="92" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
           <t>L-3</t>
@@ -2301,22 +2301,22 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>删仿真对简报（brief）历史数值的影响未量化</t>
+          <t>历史简报使用最新重介灰分</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>brief.py 走 resolvers（同样不再含仿真），但简报金标准 backend/data/brief_js.json 未重新生成；而金标准路径里密度层是默认值 → 仿真本来就被门控关掉 → **金标准对这次改动不敏感**。</t>
+          <t>原先在小时循环外解析当前重介灰分，套用全部历史小时。</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>等于这次语义变更在简报这条链上「既没被验证、也没被守卫」。若某段历史里密度是真实来源（手动/实测录入），简报数值与改动前会不同，而没有任何断言覆盖；简报是现场每天看的东西，出错不易察觉。</t>
+          <t>新增未来采样会改写过去的总灰分和建议密度。</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>① 用真实库快照跑一次 dump_brief_js.js + test_brief 对拍，明确「哪些行/列变化、变化多少」，把差异写进文档；② 补一条密度层为真实来源的简报用例（覆盖被门控打开的那条路径）。</t>
+          <t>按时间逐小时取当时灰分；采样与两条皮带各自记录时间，超过 24 小时则不续传；缺项留空。</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -2326,11 +2326,11 @@
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>本次只跑了 7 个 E2E + pytest；金标准文件（backend/data/*.json）未被重新生成</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
+          <t>已修复。更新 24 行合成金标准；新增未来采样不改历史、各通道独立过期测试。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="92" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
           <t>L-8</t>
@@ -2338,22 +2338,22 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>「调密度→看灰分怎么走」的演示能力随仿真消失</t>
+          <t>灰分来源与时间不一致</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>删仿真后，调密度的效果只在新化验/新仪表数据到达后才会体现（这正是新语义的本意），但界面上除了来源列改成「自动(502测量)」与采集页 tooltip 外，没有别的地方说明这一点。</t>
+          <t>总灰分人工输入时，事实提示仍读取 501 来源及 502 时间；补录字段名也有误。</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>现场培训/演示时那条链看起来是「死的」；操作员也可能误以为系统没反应 —— 这与 9-12 那次「改了化验建议不动」被误读是同一类风险（当时靠卡片副标题与详情弹窗讲清楚才解决）。</t>
+          <t>人工值可能被标为默认值，录入时间与测量时间混淆。</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>① 在合并系统卡片副标题或详情弹窗补一句「调密后需等新化验/新仪表数据」；② 若确需演示，另做一个**明确标注为仿真**的沙盘模式，不参与任何真实计算与决策日志。</t>
+          <t>按当前生效来源生成提示，区分测量与录入时间；未知时间明确显示未知。调密后继续等待新实测。</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -2363,11 +2363,11 @@
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>本轮前端文案改动仅覆盖来源列与采集页 tooltip；卡片侧暂无同类提示</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
+          <t>已修复。人工总灰分、公式核算与灰分密度导入的来源测试通过。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="92" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
           <t>L-5</t>
@@ -2375,22 +2375,22 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>仿真残留配置与函数未清理（易误导后来者）</t>
+          <t>仿真残留清理</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>删仿真后，前端仍保留 DENSITY_GUIDE.simBaseRho / simK、getSimBaseRho()，并在 app.js:1775 一行里对外暴露；后端 density.py 的 DENSITY_GUIDE 也仍带 simBaseRho / simK。</t>
+          <t>旧仿真参数可能被误认为仍在生效。</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>后来者读到会以为仿真还在（甚至照着它「恢复」），也可能有人误用这两个常数去估算增益；同时它是「同一口径两份实现」的潜在分叉点（前后端各一份现已无用的定义）。</t>
+          <t>维护人员可能误用仿真常数。</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>删除，或明确标注为历史（例如「2026-09-21 起仿真已移除，仅保留供旧数据解读」）；把 app.js:1775 那处对外暴露一并清掉；两处同时改，避免只删一侧。</t>
+          <t>保留已完成的仿真清理；灰分响应只使用新化验或仪表数据。</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
@@ -2400,11 +2400,11 @@
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
-          <t>grep 实测：app.js:1672-1676 / 1756 / 1764 / 1775；density.py:33-34</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
+          <t>此前已完成，本轮继续验证调密不伪造灰分响应。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="92" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
           <t>L-6</t>
@@ -2412,22 +2412,22 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>两个同名文档生成器并存</t>
+          <t>文档生成入口统一</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>generate_optimization_plan_xlsx.py（Codex 包装器）与 .mjs（真正的构建器）同目录同名。</t>
+          <t>旧 Python 包装器与 JS 实现并存。</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>将来改文档只改一个就会漂移，也无法一眼判断哪个是权威来源。</t>
+          <t>只修改一处会导致文档漂移。</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>与 L-1 合并处理：openpyxl 版作为唯一生成入口；.mjs 移到 docs/tools/ 或删除并留说明。</t>
+          <t>仓库 Python 生成器作为持续维护入口。</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
@@ -2437,11 +2437,11 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>两文件分别 1641 / 11749 字节</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
+          <t>此前已完成；本轮状态更新由统一 JSON 输入复现。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="92" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
           <t>L-7</t>
@@ -2475,6 +2475,191 @@
       <c r="G11" s="12" t="inlineStr">
         <is>
           <t>报告文件：docs/项目优化与后续计划-20260921.xlsx（4 Sheet，含编号对照）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="92" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>L-9</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>采样仅本地保存</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>整库镜像不拥有采样表，原补录没有调用采样追加接口。</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>换浏览器后看不到采样，后端无法积累学习数据。</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>追加接口保存唯一客户端标识，失败保留待发记录，重试去重；快照返回已保存采样。</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
+        <is>
+          <t>已修复。重复提交、断网重试、镜像不删除采样、非法采样输入均有回归。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="92" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>L-10</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>相同数量的旧快照覆盖新修改</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>记录数守卫无法识别等数量的内容或设置变更。</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>多个浏览器可能静默覆盖彼此修改。</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>GET 返回版本，PUT 校验版本并原子写入；前端等待初始同步，串行发送，冲突保留副本。</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>已修复，对应 D-4/T-10。旧版无版本客户端被拒绝写入，需刷新页面后核对数据。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="92" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>L-11</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>501/502 同时刻记录互相覆盖</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>导入覆盖键和数据库唯一约束缺少皮带字段。</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>补齐 501 数据后可能覆盖同系统同时间的 502。</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>前端覆盖键、后端 upsert 与唯一索引加入皮带；SQLite 启动升级保留历史行。</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>已修复。双皮带并存和旧结构升级均在临时数据库验证；现场库尚未执行升级。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="92" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>L-12</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>模型验证提前使用验证数据</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>原填补均值、标准化及目标均值在全数据上计算；时间验证复用全局选出的分量数。</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>交叉验证分数可能偏乐观，生产模型选择依据失真。</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>每个训练折独立预处理并选参数；时间验证传入原始缺失值；前后端同步更新。</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t>已修复。JS/Python/sklearn 对拍与独立单特征逐折验证通过；现场模型未自动重训。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="92" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>L-13</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>501/502 煤量是否重叠</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>项目描述 501 为总混配、502 为重介，但部分总量仍将两者相加。</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>若 501 已包含 502，会重复计量并影响目标重介灰分。</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>请现场确认包含或互斥关系，再统一实时公式与历史简报；确认前保留现有口径。</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>尚未修改物料公式。缺少现场计量关系，不能凭代码注释确定。</t>
         </is>
       </c>
     </row>
@@ -3187,12 +3372,12 @@
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>与现场确认 501 灰分仪的读数是否可导出/可抄录；确认后在表3 增加 501 行（或独立列），前端与后端取值链已支持 belt='501'（brief 第 6 列、resolve_total_ash 均已就绪），无需改代码</t>
+          <t>代码侧已修复同系统、同时间的 501/502 记录互相覆盖；前端导入、后端 upsert 与唯一索引均包含皮带。仍需现场提供 501 灰分，不能用默认常量补造。</t>
         </is>
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>现场配合（代码 0）</t>
+          <t>代码已修复；现场数据待提供</t>
         </is>
       </c>
       <c r="J15" s="7" t="inlineStr">
@@ -4208,17 +4393,17 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>口径确认：501 无在线值时，总灰分兜底取什么？</t>
+          <t>Q-4 已决：默认常量不驱动密度建议</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>与 T-12 相关但属口径选择：① 用 502 推算 ② 保持常量 8.8 但界面标注「默认常量」而非「仪表」。在 501 数据到位前，这条决定界面显示什么。</t>
+          <t>原口径问题已落地。仍需要 T-12 的真实 501 灰分；新增煤量关系待确认见 L-13。</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>决定后约 30 分钟可完成（涉及 resolve_total_ash 兜底与层级文案）。</t>
+          <t>已完成代码；待提供实测数据</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -4555,7 +4740,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>待决</t>
+          <t>已决：方案D</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
@@ -4575,7 +4760,7 @@
       </c>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>【2026-09-11 修正：原先建议的方案B 经实现前核查**不成立**，已撤回】关键事实：GET /api/v1/state 只返回 24 个键，**不含** manualEntries / importLogs / alerts / regressionModels / heavySamples —— 浏览器永远拿不到服务器上的这些行；而后端除 /manual-entries 的 POST（前端无调用者）外没有任何地方写 Alert / ImportLog，这些表**只由浏览器整库镜像写入**。把这类表纳入守卫，等于让守卫去比较一个两端**不可能收敛**的集合：只要某台浏览器的列表比服务器短，它的每一次镜像都会被拒，而它永远无法通过 GET 补上缺失的行 → **永久拒写**，正是缺陷 M-1 的病理。alerts 还更特殊：checkAlerts() 每次刷新都重建该数组（派生值，合法变少），纳入守卫会在告警消失时立刻开始拒写。另注：force=true 会连 heavy_samples 一起整体重写，所以「显式清空走 force」在支持**按表 force** 之前也不能直接用。因此可行的是方案C（前端逐条上行，镜像不再拥有这些表）或方案D（服务器只增不删/按 ts 合并）。【已决 2026-09-11：采用方案D 并已实现】migrate.replace 对 force=False 不再 wipe 这些表，改为按自然键合并（manual_entries: ts+category；import_logs: ts+category+filename；alerts: ts+system+message；regression_models: model_type+created_at；coarse_model_history: trained_at+production），只插入库里没有的行、**不删除**任何已有行；force=true（备份恢复）仍是整体覆盖。真实库实证：发送 manualEntries/alerts/importLogs 全为空的镜像后，服务器的 manual_entries 242 / alerts 1 / import_logs 3 **一条不少**。代价（已知并接受）：界面「清空补录历史」不再删除服务器侧历史行——若要在界面上真正清服务器，需要单独的 force 入口（见 M-7 的后续项）。</t>
+          <t>方案D 已于 2026-09-11 实现：审计类记录按自然键合并、只增不删。2026-09-21 补充：重介采样通过独立接口追加并支持重试，GET /state 返回采样；整库镜像仍不删除采样。覆盖型表另由版本号检测并发修改。</t>
         </is>
       </c>
     </row>
@@ -4705,17 +4890,17 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>引入 revision 让「新者胜」（彻底替换「多者胜」）</t>
+          <t>D-4 已启动并完成，见 L-10</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>这是比 T-6 更彻底的解法，但需要同时改后端表结构、PUT /state 契约与前端判据，属架构级改动；而 T-6 的向量比较已能覆盖当前已知的洗库通道。先用低成本方案堵住已知缺口，等实测再出现「数量多但内容旧」的真实案例再上 revision。</t>
+          <t>已复现相同记录数下旧浏览器覆盖新修改。覆盖型表使用内容版本，比较版本与写入位于同一 SQLite 事务。</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>T-6 上线后仍出现误判，或需要多端并发写入时。</t>
+          <t>不再暂缓。冲突保留本地副本，先导出并核对，再恢复服务器数据。</t>
         </is>
       </c>
     </row>
